--- a/src/attributions/attributions_ig_traj_492.xlsx
+++ b/src/attributions/attributions_ig_traj_492.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG8"/>
+  <dimension ref="A1:GG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,55 +999,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.8028564595594359</v>
+        <v>0.2619550497750357</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1110635025382815</v>
+        <v>-0.08673081656262269</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1403735680547751</v>
+        <v>-0.06223600056134439</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1299249244812624</v>
+        <v>0.05614325619610833</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1762004810005236</v>
+        <v>0.130595770041094</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.004487092448890202</v>
+        <v>0.002862205177806196</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>-0</v>
@@ -1056,16 +1056,16 @@
         <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1357423251143779</v>
+        <v>0.03900451934011692</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001974223163665802</v>
+        <v>0.0367592707347984</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.08543988321875541</v>
+        <v>6.04136388937675e-05</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1077,22 +1077,22 @@
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.09581721237760905</v>
+        <v>0.1147075550825692</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.01499417862661518</v>
+        <v>-0.1039255596779642</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1539597350549649</v>
+        <v>0.2089627761290752</v>
       </c>
       <c r="AG2" t="n">
         <v>-0</v>
@@ -1107,22 +1107,22 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.2202389513058111</v>
+        <v>0.1210141983888053</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.1624955815547861</v>
+        <v>-0.04669825489545797</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1681017792330272</v>
+        <v>0.2068005362277343</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -1137,181 +1137,181 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-1.057597329632674</v>
+        <v>0.3639887140748443</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1244999675892979</v>
+        <v>-0.3320718905734232</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.2155907846347875</v>
+        <v>-0.1082948403501068</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB2" t="n">
         <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.1135927233288009</v>
+        <v>-0.007693179010534474</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.01612088436063738</v>
+        <v>-0.004990755716559945</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1294484294339311</v>
+        <v>-0.00468497289578209</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.212865705964078</v>
+        <v>-0.05026996077639711</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.1240178637643221</v>
+        <v>-0.00720787682682621</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.2448567717438226</v>
+        <v>0.1157120806253278</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.6808410771664982</v>
+        <v>0.1703976404613828</v>
       </c>
       <c r="BW2" t="n">
         <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.01713090540759722</v>
+        <v>-0.118180558812997</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.1810600731328285</v>
+        <v>-0.02086592135907191</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.3160408607036775</v>
+        <v>-0.1858065865322598</v>
       </c>
       <c r="CF2" t="n">
         <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.1008766152899579</v>
+        <v>0.130314039138462</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.09332401892249033</v>
+        <v>0.03294266048123701</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
         <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.1268122613870505</v>
+        <v>-0.155243724239111</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.2316676443741003</v>
+        <v>0.08658746126482994</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.7134061013548108</v>
+        <v>-0.02523660572061446</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.3526613539869076</v>
+        <v>-0.2157013834537162</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.1388358915509712</v>
+        <v>0.1430543832119766</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.05979857534124931</v>
+        <v>0.05843742500197314</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
@@ -1326,70 +1326,70 @@
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.3753248203398122</v>
+        <v>-0.210389897796812</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.1774080412554298</v>
+        <v>0.0699358750606198</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07754623152603042</v>
+        <v>-0.02740820525146153</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.3377308579990799</v>
+        <v>-0.1487562152443873</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.1406065138411741</v>
+        <v>0.1351724307007736</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.1730947635943993</v>
+        <v>-0.101404784694289</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.2791707348437766</v>
+        <v>-0.08936980889832405</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.2740539199531737</v>
+        <v>0.01313839472941369</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.006827215670192816</v>
+        <v>-0.002762656209090924</v>
       </c>
       <c r="EB2" t="n">
         <v>-0</v>
@@ -1401,28 +1401,28 @@
         <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.3396790669000531</v>
+        <v>-0.1739837339015279</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0.1119195185529579</v>
+        <v>0.1131918193178688</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.1892698410694338</v>
+        <v>0.06779403222226622</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
@@ -1434,16 +1434,16 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.112350773915924</v>
+        <v>0.03456041957348385</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.1025734900384906</v>
+        <v>0.05698454138630499</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.05115694418410444</v>
+        <v>-0.07083488416471516</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
@@ -1452,34 +1452,34 @@
         <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.3478192022580748</v>
+        <v>-0.23507009317709</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.1192219312932432</v>
+        <v>0.1436176641144985</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.115299014819442</v>
+        <v>0.03228977329884256</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
         <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
         <v>-0</v>
@@ -1488,16 +1488,16 @@
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.015436499341557</v>
+        <v>-0.08528839192977845</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.01104669284893606</v>
+        <v>-0.037766531204624</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.09365964789003077</v>
+        <v>-0.007475688819291966</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
@@ -1515,63 +1515,63 @@
         <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.1666556281315017</v>
+        <v>-0.1763695939316243</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.394431247205838</v>
+        <v>0.3060311223118352</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.1652879981090217</v>
+        <v>0.09273393987708498</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.07664241769766392</v>
+        <v>-0.1897974982115776</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.03352310750991177</v>
+        <v>0.02614515162208319</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.1859663838370866</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.4571911604808987</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,88 +1580,88 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>-0.1195685118151169</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0.3215972025033521</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.02055823409454223</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.1241081876008069</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.04298286539358182</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0.03141918149269042</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.02394794003173123</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.07413266994180365</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>-0.1829756168653683</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0.1235689799157545</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.01177474675235598</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.1811675728669127</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>0.06791851129731934</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1670,79 +1670,79 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.321317344950868</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0.09416254336815064</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.19409722252426</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.04701373688731739</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0.08551891083043689</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0.05285930389707992</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.7335724054090038</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>-0.0393816068635148</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0.3238331521725486</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.01280682666516479</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.01668185220776464</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>0.032036997378715</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>-0.1163242448037645</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.1426784078080035</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.1185831934439978</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.3635222173765445</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
@@ -1778,55 +1778,55 @@
         <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>0.2635618082030619</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0.09267335796506743</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>0.4443647405831468</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>-0.3166321851660936</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
         <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0.5062255919756817</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.1311767117338827</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0.2961508468403704</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>0.03748494548616567</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
@@ -1835,13 +1835,13 @@
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>0.2242708464315985</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0.08137589453566312</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>-0.6089422684827198</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
@@ -1850,25 +1850,25 @@
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.3546779662484097</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
         <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>0.2295242993216255</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.1001076829287222</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0.3053255711293991</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
@@ -1877,133 +1877,133 @@
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.01994853810197775</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>0.2586845166752291</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.02605991242658765</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>-0.5001094965764262</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.4334406223389364</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>0.1490040820252676</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.009362498313444276</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>-0.2352115082951561</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>0.06018262278022304</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>0.05232544060393587</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>-0.03971633667159934</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>-0.3078438513743152</v>
       </c>
       <c r="DY3" t="n">
         <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>-0.3046063812629549</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0.1264664634972594</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.2144068285010506</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0.1355224773827653</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0</v>
+        <v>-0.02597695090845792</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>0.1928018762800312</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.1036828235723479</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>-0.08113758450513837</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
@@ -2012,10 +2012,10 @@
         <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.08837433321779614</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU3" t="n">
         <v>0</v>
@@ -2024,25 +2024,25 @@
         <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>0.02752963211540562</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.1483906243628409</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>-0.3668915746559359</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA3" t="n">
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>0.007159687140136515</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2051,22 +2051,22 @@
         <v>0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>0.2825658119616218</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.009501584868016865</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0.2621387544247666</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0</v>
+        <v>0.05472604804687038</v>
       </c>
       <c r="FL3" t="n">
         <v>0</v>
@@ -2078,13 +2078,13 @@
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>0.2796335972554967</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.183852340586709</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0.2806777494377605</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,28 +2093,28 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>0.5225872636653365</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>0.03329326727189778</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.231817261532248</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>-0.2552246850639061</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
         <v>0</v>
@@ -2126,13 +2126,13 @@
         <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>0.4486633017844044</v>
       </c>
     </row>
     <row r="4">
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.2435851852636869</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,16 +2149,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0.05385059566260353</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>-0.1847458306153997</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.06546562658804223</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,43 +2176,43 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.000482231631598978</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.03724466791631605</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.04732237220682321</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0</v>
+        <v>-0.02479907162012457</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0.006755685075473581</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>-0.007901084961814062</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -2230,16 +2230,16 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0</v>
+        <v>-0.03390621376267427</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0</v>
+        <v>0.01007139681778743</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.09914948724889754</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,16 +2257,16 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0</v>
+        <v>0.06960218333089967</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0</v>
+        <v>-0.05475576611132885</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>0.4182993168309648</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2284,25 +2284,25 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0</v>
+        <v>0.01713127506814209</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>-0.105353475192189</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>-0.002099714834306692</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,16 +2311,16 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>-0.005868403462818047</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0</v>
+        <v>-0.06536049409907763</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,25 +2329,25 @@
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>-0.004014966198510842</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0</v>
+        <v>0.1039664929245113</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0.04443117616131183</v>
       </c>
       <c r="BR4" t="n">
         <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
@@ -2356,46 +2356,46 @@
         <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>0.1996318749834025</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0</v>
+        <v>0.01454625279841814</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>-0.1205120140986078</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0</v>
+        <v>-0.1380825244251891</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0</v>
+        <v>-0.02807146344007655</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0</v>
+        <v>0.0984687751467011</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
@@ -2404,58 +2404,58 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0</v>
+        <v>-0.09538981741942935</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0</v>
+        <v>-0.01499497991331313</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0</v>
+        <v>0.129365469470432</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0</v>
+        <v>-0.1369028446511188</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0</v>
+        <v>-0.02555717594962167</v>
       </c>
       <c r="DA4" t="n">
-        <v>0</v>
+        <v>0.1124087544025432</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
         <v>0</v>
@@ -2464,19 +2464,19 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0</v>
+        <v>-0.07626904249842409</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0</v>
+        <v>-0.1170373591476589</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0</v>
+        <v>0.06334108540078673</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,67 +2485,67 @@
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0</v>
+        <v>-0.04972897889185935</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0</v>
+        <v>-0.06923391295760907</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0</v>
+        <v>-0.1056513684559165</v>
       </c>
       <c r="DT4" t="n">
         <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0</v>
+        <v>-0.07579922202559297</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0</v>
+        <v>-0.0499362651428659</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>0.08352022888146382</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0</v>
+        <v>-0.0921301315233977</v>
       </c>
       <c r="EH4" t="n">
         <v>0</v>
@@ -2554,64 +2554,64 @@
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0</v>
+        <v>-0.04952751172703645</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0</v>
+        <v>0.06017511602945008</v>
       </c>
       <c r="EL4" t="n">
         <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
         <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0</v>
+        <v>0.01730020071195064</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0</v>
+        <v>0.04921664998717266</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0.03853956635667437</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>0</v>
+        <v>-0.1547140506830637</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0</v>
+        <v>-0.06694104254323663</v>
       </c>
       <c r="FC4" t="n">
-        <v>-0</v>
+        <v>0.09040635637768661</v>
       </c>
       <c r="FD4" t="n">
         <v>0</v>
@@ -2620,13 +2620,13 @@
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0</v>
+        <v>-0.1176730564085872</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0</v>
+        <v>0.04432109970638235</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0.05735178371556526</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2650,55 +2650,55 @@
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0</v>
+        <v>-0.2141001028542203</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0</v>
+        <v>-0.1180855080195521</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>-0.05590236164565082</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
         <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0</v>
+        <v>-0.07547576825115057</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0</v>
+        <v>0.03846033563864265</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>0</v>
@@ -2709,73 +2709,73 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.320612461313824</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.1253475631420793</v>
       </c>
       <c r="E5" t="n">
-        <v>-0</v>
+        <v>-0.0369117316837423</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.1055998638087183</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.03848390480580444</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.01422768811142956</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.07457515008816537</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.01366606875642281</v>
       </c>
       <c r="W5" t="n">
-        <v>-0</v>
+        <v>-0.01016338926773356</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -2787,22 +2787,22 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.1254562094334109</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-0.1489842631321454</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0</v>
+        <v>0.1975541687280803</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2817,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>0.1484902216074274</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>-0.06756149429193763</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0</v>
+        <v>0.1452853742872595</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2838,55 +2838,55 @@
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>0.4750989472325332</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0.2485755777933361</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0</v>
+        <v>-0.1386213113023159</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>-0.02121864878835282</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>-9.284419662844092e-12</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0</v>
+        <v>-0.01094332407025997</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
@@ -2895,46 +2895,46 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>-0.02189936688294825</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>0.05236765674023114</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0</v>
+        <v>0.09469136209018929</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR5" t="n">
         <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>0.2292439317904562</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>-0.09476686939220186</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0</v>
+        <v>-0.004237054638506449</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -2952,19 +2952,19 @@
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0</v>
+        <v>-0.1792217170081273</v>
       </c>
       <c r="CF5" t="n">
         <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>0.1399158112472531</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0</v>
+        <v>-0.011134311877085</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2973,58 +2973,58 @@
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0</v>
+        <v>-0.1472179470350052</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>0.09383105153919939</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0</v>
+        <v>-0.05211343739794598</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0</v>
+        <v>-0.181227245148259</v>
       </c>
       <c r="CX5" t="n">
         <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0</v>
+        <v>0.1422249285507935</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0</v>
+        <v>0.00396385199925203</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0</v>
+        <v>-0.07114579231986876</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>0.04487931027868647</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0</v>
+        <v>-0.02237354648000213</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,31 +3054,31 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0</v>
+        <v>-0.1379506528047534</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0</v>
+        <v>0.1297300320674825</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0</v>
+        <v>-0.1283311921179802</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
@@ -3087,19 +3087,19 @@
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0</v>
+        <v>-0.09048057287916254</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0.06554483741106151</v>
       </c>
       <c r="EA5" t="n">
-        <v>0</v>
+        <v>0.03043895244809514</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
@@ -3108,22 +3108,22 @@
         <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0</v>
+        <v>-0.1781739891272124</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>0.1535218333996262</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0</v>
+        <v>0.02723818588817496</v>
       </c>
       <c r="EK5" t="n">
         <v>0</v>
@@ -3135,22 +3135,22 @@
         <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0</v>
+        <v>0.04903745358662805</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0</v>
+        <v>0.01364416100864323</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0</v>
+        <v>-0.08147446696529687</v>
       </c>
       <c r="ET5" t="n">
         <v>0</v>
@@ -3162,25 +3162,25 @@
         <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0</v>
+        <v>-0.2132819672611505</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>0.1513600812291186</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0</v>
+        <v>-0.01310350468181252</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
@@ -3189,49 +3189,49 @@
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0</v>
+        <v>-0.03150646756295217</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>0.03654580898159204</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0</v>
+        <v>-0.07071825729449835</v>
       </c>
       <c r="FL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0</v>
+        <v>-0.3333259728779917</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0</v>
+        <v>0.2450238413464066</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0</v>
+        <v>0.1162502035965022</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
@@ -3249,25 +3249,25 @@
         <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0</v>
+        <v>-0.1781264365692551</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>0.07501903394092216</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3275,55 +3275,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.008702442315977468</v>
+        <v>-0.171240446356537</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0.007680964147801026</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01412986220321806</v>
+        <v>0.001774963461866562</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1613061118819656</v>
+        <v>0.2575704440972199</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.002443639229718022</v>
+        <v>-0.09857613410827064</v>
       </c>
       <c r="L6" t="n">
         <v>-0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0</v>
+        <v>0.001331787859859038</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.001191431538102316</v>
+        <v>0.02542949014305649</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.02096353202940704</v>
+        <v>0.06809977886806327</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -3332,52 +3332,52 @@
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.03021371917478426</v>
+        <v>-0.01624875175754235</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.004654172021112564</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.03429929994148333</v>
+        <v>-0.04423755731240923</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.04035177253040109</v>
+        <v>0.08921323596965784</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.01914312051050816</v>
+        <v>-0.04277190316487935</v>
       </c>
       <c r="AD6" t="n">
         <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0.1612784832829536</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.07124827561606777</v>
+        <v>-0.05751262214786013</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.008449023479097689</v>
+        <v>-0.1014907951410932</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -3386,49 +3386,49 @@
         <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.02438775926293604</v>
+        <v>-0.139116286259581</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>-0.03007065014746551</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.002838984740748366</v>
+        <v>-0.2045361637688692</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.08817585804232592</v>
+        <v>0.09333026831069377</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT6" t="n">
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.03755345867435549</v>
+        <v>-0.4227276689593316</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.04099799359568775</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.1448293623872901</v>
+        <v>-0.06328571466346673</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.2735537328307367</v>
+        <v>0.3405725119742771</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3440,19 +3440,19 @@
         <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.01549404261685033</v>
+        <v>0.08146158731767851</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0</v>
+        <v>0.04814661351185487</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.001203646081477343</v>
+        <v>0.03152504372537294</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.01370883443713902</v>
+        <v>0.01032501039180341</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
@@ -3461,25 +3461,25 @@
         <v>-0</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>-1.273737720837747e-10</v>
+        <v>0.01511483408290182</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>0.04392388964071998</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.04141823314911543</v>
+        <v>-0.06891004307088978</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.03489293329313189</v>
+        <v>-0.01027170488163291</v>
       </c>
       <c r="BR6" t="n">
         <v>0</v>
@@ -3491,49 +3491,49 @@
         <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.03667518503313495</v>
+        <v>-0.07900533723368132</v>
       </c>
       <c r="BW6" t="n">
         <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>-0.03558920818210225</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.05216711328477238</v>
+        <v>-0.03078910054110617</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.104231710817916</v>
+        <v>0.2907938952955388</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
         <v>-0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.02497130768386074</v>
+        <v>0.1844816023422219</v>
       </c>
       <c r="CF6" t="n">
         <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0.01000176369043809</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.001245180742946756</v>
+        <v>0.01213307232745908</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.08241730686940162</v>
+        <v>-0.1166126909380744</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
@@ -3545,25 +3545,25 @@
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.02794808476573735</v>
+        <v>0.131038666803369</v>
       </c>
       <c r="CO6" t="n">
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>-0.1331858462785224</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.08535516033147073</v>
+        <v>-0.06818136171292137</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.002681862500311998</v>
+        <v>-0.1673999944558228</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
@@ -3572,22 +3572,22 @@
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.003479225807909342</v>
+        <v>0.2026040927709042</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0</v>
+        <v>-0.0163697717019878</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.00085274219695125</v>
+        <v>-0.04402954579275797</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.08614548258123109</v>
+        <v>-0.1284190606027756</v>
       </c>
       <c r="DB6" t="n">
         <v>-0</v>
@@ -3596,52 +3596,52 @@
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.07966942049195158</v>
+        <v>0.06456057343112241</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0</v>
+        <v>-0.01494318952788969</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.03538465950278699</v>
+        <v>-0.01634651706472356</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.004202127406225238</v>
+        <v>-0.09874741595565589</v>
       </c>
       <c r="DK6" t="n">
         <v>-0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM6" t="n">
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.04961535914346125</v>
+        <v>0.09574365653671719</v>
       </c>
       <c r="DP6" t="n">
         <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>-0.03628488701455816</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01470568501656794</v>
+        <v>0.0666855830127767</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.001724702832931302</v>
+        <v>-0.04170811827398051</v>
       </c>
       <c r="DT6" t="n">
         <v>0</v>
@@ -3650,52 +3650,52 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.02574094534458133</v>
+        <v>0.145032617666855</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0</v>
+        <v>0.07374294498819463</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.070709530941992</v>
+        <v>0.04511136704592579</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.007104029540025072</v>
+        <v>0.1863036060800307</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.01543969028750585</v>
+        <v>0.1807666325127222</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0.04347295330007458</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0009366872380012053</v>
+        <v>-0.06020174842665267</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.113277145555773</v>
+        <v>-0.02213649461145596</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
@@ -3704,112 +3704,112 @@
         <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.05279508505179564</v>
+        <v>-0.04141193999515907</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>0.03604270280854751</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.06525048176892423</v>
+        <v>0.06066853868704446</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.01007532550676187</v>
+        <v>-0.0443592548080016</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0163201665252518</v>
+        <v>0.2152405797646223</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0</v>
+        <v>-0.02135235971286058</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.02062765040185204</v>
+        <v>0.0001299532401841634</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.08536027545926277</v>
+        <v>-0.1415746655259038</v>
       </c>
       <c r="FD6" t="n">
         <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.002411073962460138</v>
+        <v>0.08588162940221374</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>-0</v>
+        <v>0.03196520293730445</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.03969726252176888</v>
+        <v>0.03020526811106625</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.1104076497114677</v>
+        <v>-0.05935240506123883</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.01871813229903468</v>
+        <v>0.1463618806873923</v>
       </c>
       <c r="FR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0</v>
+        <v>-0.1740009801660858</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.1110295586717076</v>
+        <v>-0.09920360599552917</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0301747221944175</v>
+        <v>-0.05342443405337463</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
         <v>-0</v>
@@ -3818,25 +3818,25 @@
         <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.0006951453670751307</v>
+        <v>0.1575826563856794</v>
       </c>
       <c r="GA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0</v>
+        <v>0.04834172968740322</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.03898031810921029</v>
+        <v>-0.08217758565000771</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3844,103 +3844,103 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.02606436647415308</v>
+        <v>0.668418671207786</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1410841232305102</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001722985874228348</v>
+        <v>0.1094415948656207</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>-0.3103059876680621</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002038632570748529</v>
+        <v>0.3372236788145391</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1486370965644891</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.001571009318324645</v>
+        <v>-0.0302346375836284</v>
       </c>
       <c r="O7" t="n">
-        <v>-0</v>
+        <v>-0.0620170550245568</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.02577903831419555</v>
+        <v>0.03122282736143071</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001720141509803735</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01338462953015175</v>
+        <v>-0.07884555711385514</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.0643033709281349</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.02909508857982442</v>
+        <v>0.1150429189795768</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.006095102860094011</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.006938169523359658</v>
+        <v>-0.1646291437120581</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>0.03129993126401888</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -3949,52 +3949,52 @@
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.02912287770403351</v>
+        <v>0.207558225564091</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.02343064859605092</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.04883787432019746</v>
+        <v>0.1208303661048009</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0</v>
+        <v>-0.2128694019620233</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.1146389953321128</v>
+        <v>0.9687696605334274</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.05883545142929949</v>
+        <v>-0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.02066686724770357</v>
+        <v>-0.3128596943389631</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>-0.2908777425999995</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0</v>
@@ -4003,28 +4003,28 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.001866769483235097</v>
+        <v>0.02638287916222523</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.04819461199030672</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.01203196465573289</v>
+        <v>-0.005592459810951391</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>-0.08182175408746846</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
         <v>-0</v>
@@ -4036,25 +4036,25 @@
         <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.18457877653566e-11</v>
+        <v>0.04698945988055202</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.008083119112589316</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>-1.809988603027532e-10</v>
+        <v>0.1867494303557978</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>0.1320703325279523</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
         <v>0</v>
@@ -4063,25 +4063,25 @@
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.02914251084311896</v>
+        <v>0.5916142374831568</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.00326791845449886</v>
+        <v>-0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.01462703792014756</v>
+        <v>-0.01348504334101385</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>-0.3406272789895132</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,106 +4090,106 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.006962128752418596</v>
+        <v>-0.356078026330242</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.02772438920980815</v>
+        <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.01754428226751912</v>
+        <v>-0.06086489585331183</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>0.2100475370936247</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>-0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.00533163560848909</v>
+        <v>-0.5235747499950906</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.01804697530539209</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.03367121672410639</v>
+        <v>0.1239655542516514</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0</v>
+        <v>0.249171547368314</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT7" t="n">
         <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.01590394948267502</v>
+        <v>-0.3427130754217542</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.0255874996878926</v>
+        <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.01242266042670541</v>
+        <v>-0.0707353443670401</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0.1845160827790845</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.03864299346484625</v>
+        <v>-0.04957513662646613</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.005365939498341055</v>
+        <v>-0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05044743377596524</v>
+        <v>-0.1164107150130752</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>0.1438058221929881</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
         <v>-0</v>
@@ -4198,19 +4198,19 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.02393067031767739</v>
+        <v>-0.1578969170837012</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.04971239870717981</v>
+        <v>-0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.02454972646713316</v>
+        <v>-0.05037909919642612</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0</v>
+        <v>0.04793754148858881</v>
       </c>
       <c r="DT7" t="n">
         <v>0</v>
@@ -4219,25 +4219,25 @@
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.03862623438178422</v>
+        <v>0.1288298809217099</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.01353509121135553</v>
+        <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.03713148971465929</v>
+        <v>0.0161939354803428</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0.03402305754262812</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4249,55 +4249,55 @@
         <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.02954340720891973</v>
+        <v>-0.1105717865615377</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.05848007383310198</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.003575607273818432</v>
+        <v>-0.1446711424610651</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0</v>
+        <v>0.1181531887853262</v>
       </c>
       <c r="EL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN7" t="n">
         <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.01255100086380578</v>
+        <v>-0.2129521498957477</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.01562331810599974</v>
+        <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.009565261628893066</v>
+        <v>-0.1815907443346481</v>
       </c>
       <c r="ET7" t="n">
-        <v>0</v>
+        <v>0.08642521192448049</v>
       </c>
       <c r="EU7" t="n">
         <v>-0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
         <v>0</v>
@@ -4306,76 +4306,76 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.01677693951783526</v>
+        <v>-0.3559439673113879</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.01810908183928798</v>
+        <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01185106469975192</v>
+        <v>-0.1276134925929389</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>0.1697496891159107</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.006597820044494843</v>
+        <v>-0.2885958812742566</v>
       </c>
       <c r="FI7" t="n">
         <v>0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.01717270031198093</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.004350645440955376</v>
+        <v>0.06163104596191594</v>
       </c>
       <c r="FL7" t="n">
-        <v>0</v>
+        <v>0.2809617422258275</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.01955493570230605</v>
+        <v>-0.0913083793831493</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.04216672806997141</v>
+        <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01675979882915738</v>
+        <v>0.01602541866974412</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0.002153588714092072</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>-0</v>
@@ -4387,25 +4387,25 @@
         <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02977423348905637</v>
+        <v>-0.178279505518106</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.03645000030463355</v>
+        <v>-0</v>
       </c>
       <c r="GC7" t="n">
         <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>0</v>
+        <v>0.0520569992097084</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG7" t="n">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-0.5873124986192619</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.4267303143533283</v>
       </c>
       <c r="E8" t="n">
-        <v>-0</v>
+        <v>-0.03516041816746789</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4437,22 +4437,22 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.3031183808092333</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.2864527555911255</v>
       </c>
       <c r="N8" t="n">
-        <v>-0</v>
+        <v>-0.01009562647374005</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -4470,19 +4470,19 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.03548658389384045</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.03327367599645964</v>
       </c>
       <c r="W8" t="n">
-        <v>-0</v>
+        <v>-0.01771407632279433</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -4491,52 +4491,52 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>-0.05254160934125848</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.0508979696146505</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0</v>
+        <v>-0.1445280468573554</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>-0.3250827992511478</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>0.06851443510600755</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0</v>
+        <v>-0.381767040856494</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>-0.4614047904919103</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.1954706927992136</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0</v>
+        <v>-0.02335099393472152</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
@@ -4578,49 +4578,49 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>-0.04372641623476339</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>0.009731242183573846</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0</v>
+        <v>0.01106138380580169</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI8" t="n">
         <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL8" t="n">
         <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>0.1905256446664551</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0.09027807604167838</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0</v>
+        <v>0.06497160523205023</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
@@ -4632,43 +4632,43 @@
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>-0.4562350887066343</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>0.2852637334089502</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0</v>
+        <v>-0.1801211713811342</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0</v>
+        <v>0.3843817784629632</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>-0.2349061120359056</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0</v>
+        <v>0.08944077440603627</v>
       </c>
       <c r="CI8" t="n">
         <v>0</v>
@@ -4683,19 +4683,19 @@
         <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0</v>
+        <v>0.3952611480062746</v>
       </c>
       <c r="CO8" t="n">
         <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0.2756477339159361</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0</v>
+        <v>0.158412431427018</v>
       </c>
       <c r="CR8" t="n">
         <v>0</v>
@@ -4710,46 +4710,46 @@
         <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>0</v>
+        <v>0.3743775089961209</v>
       </c>
       <c r="CX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0</v>
+        <v>-0.2187497411689928</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0</v>
+        <v>0.04969744492164523</v>
       </c>
       <c r="DA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0</v>
+        <v>0.01701525880775753</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0</v>
+        <v>-0.03852543992300856</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0</v>
+        <v>0.04717566943728845</v>
       </c>
       <c r="DJ8" t="n">
         <v>0</v>
@@ -4758,28 +4758,28 @@
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM8" t="n">
         <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0</v>
+        <v>0.2186679831757331</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>-0.1832043276560523</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0</v>
+        <v>0.03264156602660485</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
@@ -4788,22 +4788,22 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0</v>
+        <v>0.2521391474765723</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>0.1557199151910849</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0</v>
+        <v>0.03850863885690483</v>
       </c>
       <c r="EB8" t="n">
         <v>0</v>
@@ -4812,61 +4812,61 @@
         <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>0</v>
+        <v>0.266447020856751</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0.2160854030724229</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0</v>
+        <v>0.007010561866850935</v>
       </c>
       <c r="EK8" t="n">
         <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0</v>
+        <v>0.3309072220795723</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>-0.1239121477467117</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0</v>
+        <v>-0.1240968303766298</v>
       </c>
       <c r="ET8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
@@ -4875,25 +4875,25 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>0</v>
+        <v>0.4025479133458388</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0.2643381066945981</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0</v>
+        <v>0.07439924726323213</v>
       </c>
       <c r="FC8" t="n">
         <v>0</v>
       </c>
       <c r="FD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF8" t="n">
         <v>0</v>
@@ -4902,16 +4902,16 @@
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0</v>
+        <v>0.04988817047105675</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0</v>
+        <v>-0.02296405182130673</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0</v>
+        <v>0.3809384824413576</v>
       </c>
       <c r="FL8" t="n">
         <v>0</v>
@@ -4929,16 +4929,16 @@
         <v>0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0</v>
+        <v>-0.01053409217542977</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0</v>
+        <v>0.04279392334671003</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0</v>
+        <v>0.06735544173072576</v>
       </c>
       <c r="FU8" t="n">
         <v>0</v>
@@ -4950,25 +4950,25 @@
         <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
         <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0</v>
+        <v>0.2620824970841404</v>
       </c>
       <c r="GA8" t="n">
         <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>0</v>
+        <v>-0.3426792308599078</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE8" t="n">
         <v>0</v>
@@ -4977,6 +4977,4558 @@
         <v>0</v>
       </c>
       <c r="GG8" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2480196191245032</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1091498808811704</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.01624090163220384</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1397121487918561</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.04364095188462017</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.03636759231674565</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.04512256002325686</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.02311722797585528</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.05859611753426583</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.04334216465182885</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.07365952448655561</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.09976039565736763</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1062493214835173</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.01766762092729093</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.06400189865934312</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.269372872915958</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.04082257200700285</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.1386459818384259</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.01389854271420984</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.003143072316893759</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.01115467689962288</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.01081645018975903</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.005152202219851124</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.0684848002764661</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.2030499101504591</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.09309638674174694</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.03756387486304871</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.09961614089121831</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.07049378808452302</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.0136144531185351</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.07397080212544703</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.09689626058650574</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.06206405383911506</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.09640619375909336</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.07465756204809958</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.01211322462081465</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.0031521605013692</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.01578856350579828</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0.04149855999820627</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.05176068197313567</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>-0.01292922111911748</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.02112525616033855</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.1013390741693707</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.03187485449463196</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>-0.0849847539563445</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.05195636844398115</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.06789803678511808</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.01234337305767304</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.04509900419669331</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.06376807422106083</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.02599878882302157</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.1016990785260824</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.07897736271605028</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.004947968904076607</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.01271355945354082</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.04387458845109814</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>-0.039852314879081</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.01150390312470273</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.08558517461889636</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>-0.008693143364083456</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.08412645984890832</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.03700191296658749</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3909568028582112</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1937452669982074</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.04434463336212787</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2687630772825008</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.08474315417933927</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.003285028250539781</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.117163008676795</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.03249348715482207</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.05139053576145961</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.09019001102258917</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.2093590403560507</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.04465947306377572</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1397851447456689</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.07295041567762867</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.1301727699328339</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.3771876618146577</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0.1775894757912143</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.1434888871369681</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.02093406094215045</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-0.04657178172291523</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.01811590133001862</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0.02794327125164596</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.02994819397745589</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.02855529886049379</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.3423170866667323</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>-0.1024757696935022</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.01509226833691604</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0.137649086910849</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.143912453616108</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-0.04413500413196935</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0.1253796372348462</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.2651763986183097</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.07569707945086228</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-0.1268250185210457</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0.1446403680915144</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.02598046117100662</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0.03458849705584878</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0.01056118041456251</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.006308867417583266</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0.05918952036934502</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0.06450553517085356</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>-0.004008177139393772</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>-0.02287570749643295</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>-0.09166382529488951</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.1034230383052112</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0.0955053399231052</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0.1199122014529262</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0.01926736141556493</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0.0994421565969673</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0.0368205294797764</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.04045483699548536</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0.1555909477653125</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0.1627628708907052</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0.05039331390542147</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0.1360339239494147</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0.1155960947846269</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0.01415595543587805</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>-0.02068490919430607</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>-0.202427780919063</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0.02637519948868827</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>-0.1138078346845221</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0.1101133850234904</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5370681850607841</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.04708948915184706</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.2870395911700246</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5045704795900485</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.08503531492241007</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.131349466063487</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.1402766360581535</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.1618320442815013</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.04350773176395894</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.02575706403416628</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.2754551950003319</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.09182443614101342</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1730088240257038</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.00403459490112738</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.164672767454466</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.6943570045647528</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.2451178689696486</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.2511314142161196</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.06869292237546068</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.05008614499831877</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.06814597960639375</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.09707020775520322</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.1125187589060039</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.0480230465503711</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.4515758981449013</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.1142563375510017</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.1768289985281593</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.2104832846613766</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>-0.002528983187233631</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.1298000847800452</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.2692579217836317</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.1878474452663849</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.1711722759746267</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.1846762291279483</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.03260751718348064</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.1298866455577359</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>-0.02555278340916859</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>-0.204008722159496</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>-0.005486637196882418</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.09798059577458387</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.03382912282453851</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.02993789017897268</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0.1334104983544906</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>-0.02911411167856278</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.04695872107604015</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.02343008948185917</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.1142737062311114</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.0615619883329024</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>-0.05906559612018617</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>-0.1281942438343799</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.1072616411011431</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.2153975739849239</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.04383784805426556</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.1089907569385536</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.1704677276138228</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.08626330646828746</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.1994751898552625</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.02075376304666554</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.000717094849815132</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.1509480033735959</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.09104508341720791</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.01260971363326839</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2190887637460218</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.02561298560839349</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.09735799100306725</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2144855434545705</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.06015383902213417</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.05588357083603692</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.0749601181238963</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.05498820481260569</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.006341773674536959</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.03026937594402034</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.1003156472780715</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.01856540319456918</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.05671768357147226</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.002250985345170795</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.07166281572354177</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.260600733895054</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.1527141146540779</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.09375971473108827</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.03134968004513132</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-0.01405647109062241</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0.02050571377837754</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.02820000062621347</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.07537759492885124</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.05590523411818404</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.1772533000357104</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.06649878026202824</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0.05829325618447161</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-0.07323707217045933</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.02115447571408692</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.05503162422202</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0.07959730949811188</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.123749638249494</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.02748132588944742</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.06695428165823629</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.01431829492072208</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.06010265757583689</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-0.02923735562791648</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.00444867327473143</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>-0.01695178344534693</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>-0.01554427421875915</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>-0.02766693036316526</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0.01567238253837893</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.04301251650733387</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>-0.03972904224619315</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>-0.0009299127130126939</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>-0.01896985741776103</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.01288698694936886</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.03814808796281619</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.03933493082011989</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>-0.01977909752895631</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.02924527394084977</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>-0.07580899610539077</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.014615537469668</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.04230250882327551</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>-0.05998557407750264</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.03739216099621845</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.05150221024783</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>-0.0176228961290037</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.004300305662291195</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.03809786622730149</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>-0.05988942885823241</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.03792235654366893</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.308583449111996</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.06192527062209207</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01498735461953067</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.05185664689824605</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.3198456912131011</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.09135091913916245</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.04573397296712753</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.02029626940387461</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.05059917837104885</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.05263384862242074</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.04258143800393476</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.001077680820561993</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.03253066924563901</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.1183596160414706</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.08822543695268807</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0.02108572316184988</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.08586135060249891</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.02906819547406346</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.0283675167964055</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.07810812017548867</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.257900128926475</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.008780708411510071</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.09612025712289184</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.06701010115427608</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.02775253653164641</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-0.05713073646784004</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.0409511720558564</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-0.00290531547128387</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.01864709931063552</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.01808764944688996</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.04635964698693548</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.008202370603085334</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.179516481625458</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>-0.02668284540454924</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.0201974966663665</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-0.04637301096795598</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.08103489040267181</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.03444664337742039</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.009141478109068617</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.01941243894213161</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.0498933738909401</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.07434972625891639</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.1024770833710632</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.06267310280627683</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.07507196893186796</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.0324433397997397</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.005222705783081388</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.02141392456550066</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0.01680172110372933</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>-0.009175471703785505</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.102113853339944</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0.002193030114721083</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0.05226764219602257</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0.001863948575360448</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0.02969551897606912</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.01933509229306346</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0.02997744876293706</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0.01281398139323518</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0.03095206221289139</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>-0.0280845613121441</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0.04140214899558255</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.0478169978515845</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.004462986385041012</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>-0.003847202969237006</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0.03257280601175631</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>-0.01615750008377971</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0.01315688088523333</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.06196449967033405</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0.08722748908207227</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0.02864950357603495</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.00320116746872369</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.01620111188833552</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>-0.036650513831045</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.04635652613020205</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>-0.001066288582849252</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.06646770958185166</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>-0.07850149577784295</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.1385218806297966</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.001211783939256736</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0.03401854326952423</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>-0.07040626759333596</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>-0.03643832265364191</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>-0.01133830769216765</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
         <v>0</v>
       </c>
     </row>
